--- a/YouTube이슈분석_개인채널_2026-08-05.xlsx
+++ b/YouTube이슈분석_개인채널_2026-08-05.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="85">
   <si>
     <t>날짜</t>
   </si>
@@ -92,37 +92,37 @@
     <t>8:19</t>
   </si>
   <si>
+    <t>본 영상은 스웨덴 리스버그 오세아나 워터파크에서 발생한 대규모 화재 참사를 다룹니다. 1,600억 원 규모의 시설이 완공을 앞두고 왜 잿더미가 되었는지 사고 경위와 폭발 원인, 그리고 이후 수습 과정을 분석하여 대형 재난에 대한 경각심과 안전 관리의 중요성을 전달하는 다큐멘터리입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 자극적인 제목과 썸네일로 시청자의 호기심을 유도하는 경향이 있으나, 실제 사고의 원인과 안전 교훈을 중점적으로 다루는 정보성 콘텐츠입니다.</t>
+  </si>
+  <si>
+    <t>▶</t>
+  </si>
+  <si>
+    <t>메타데이터+자막(Gemini)</t>
+  </si>
+  <si>
+    <t>장애인 19명을 살해한 남자…사형 확정 뒤 그와 결혼한 여자가 나타났다｜일본 야마유리엔 사건 【일사사】</t>
+  </si>
+  <si>
+    <t>테가미 | 일본 사건사고</t>
+  </si>
+  <si>
+    <t>2026-07-30</t>
+  </si>
+  <si>
+    <t>17:52</t>
+  </si>
+  <si>
     <t>-</t>
   </si>
   <si>
-    <t>스웨덴 리스버그의 1600억 원 규모 오세아나 워터파크가 건설 중 발생한 대규모 화재로 전소된 사건을 다룹니다. 영상은 화재의 발단과 폭발 원인을 분석하고, 대형 시설 건설 현장에서의 안전 관리 및 예방의 중요성에 대한 교훈을 전달하며 사고 이후의 상황을 정리합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 달리 영상은 실제 사고의 경위와 안전 교훈을 전달하는 다큐멘터리 형식을 취하고 있습니다.</t>
-  </si>
-  <si>
-    <t>▶</t>
-  </si>
-  <si>
-    <t>메타데이터+자막(Gemini)</t>
-  </si>
-  <si>
-    <t>장애인 19명을 살해한 남자…사형 확정 뒤 그와 결혼한 여자가 나타났다｜일본 야마유리엔 사건 【일사사】</t>
-  </si>
-  <si>
-    <t>테가미 | 일본 사건사고</t>
-  </si>
-  <si>
-    <t>2026-07-30</t>
-  </si>
-  <si>
-    <t>17:52</t>
-  </si>
-  <si>
-    <t>2016년 일본 사가미하라의 장애인 시설 '쓰쿠이 야마유리엔'에서 발생한 대규모 살인 사건을 다룹니다. 범인 우에마츠 사토시는 장애인 19명을 살해하고 다수를 다치게 한 흉악범으로, 범행 동기와 과정, 재판 결과 및 사형 선고 후 옥중 결혼이라는 충격적인 근황까지 사건 전반을 상세히 재구성하여 사회적 파장을 조명합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 흉악 범죄를 다루며 자극적인 소재를 포함하고 있으므로 시청 시 정서적 주의가 필요합니다.</t>
+    <t>2016년 일본 가나가와현 장애인 시설 '쓰쿠이 야마유리엔'에서 발생한 흉악 범죄 사건을 다룹니다. 범인 우에마츠 사토시가 저지른 대규모 살상 사건의 전말과 범행 동기, 재판 과정, 그리고 충격적인 옥중 결혼 소식까지 사건의 사회적 충격과 여파를 객관적으로 정리하여 기록한 영상입니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 본 영상은 강력 범죄를 소재로 하므로 자극적인 내용에 유의하여 시청하시기 바랍니다.</t>
   </si>
   <si>
     <t>일본</t>
@@ -137,10 +137,10 @@
     <t>19:01</t>
   </si>
   <si>
-    <t>본 영상은 헤노코 앞바다에서 발생한 선박 전복 사건을 다루며, 학교 측의 심각한 안전 배려 의무 위반을 지적한 제3자 보고서 내용을 분석합니다. 피해 학생의 코스 변경 요청이 묵살된 정황과 조직의 기능 부전 실태를 짚어보며, 교육 기관으로서의 책임 의식 부재를 비판적으로 논평합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 제목과 달리 실제로는 제3자 보고서의 공식 조사 결과를 바탕으로 교육 기관의 안전 관리 책임 문제를 냉철하게 분석한 교육적 성격의 영상입니다.</t>
+    <t>본 영상은 헤노코 앞바다에서 발생한 전복 사고를 다룬 제3자 조사 보고서를 분석합니다. 학교 측의 심각한 안전 배려 의무 위반과 사고 발생 경위를 상세히 짚어보며, 학생들의 항의와 코스 변경 요청이 묵살된 구조적 문제와 학교의 기능 부전 실태를 비판적으로 고찰합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 사건의 자극적인 측면보다는 보고서가 지적한 조직적 안전 관리의 허점과 책임 소재를 중심으로 시청하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>被害者が悪すぎて加害者に同情してしまう事件【2ch事件スレゆっくり解説】</t>
@@ -155,10 +155,10 @@
     <t>12:34</t>
   </si>
   <si>
-    <t>이 영상은 2ch(현재 5ch) 스레드에서 화제가 된 사건을 '윳쿠리' 해설 형식으로 다룹니다. 피해자가 오히려 가해자에게 동정을 유발할 정도로 극심한 악행을 저질러 사회적 파장을 일으켰던 사건의 전말과 갈등 과정을 심도 있게 분석하며, 시청자들에게 사건의 이면과 인간 관계의 복잡성을 전달합니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 범죄 및 갈등 사례를 다루는 클릭베이트 성격의 콘텐츠이므로 사건의 사실관계 확인보다는 흥미 위주의 시청을 권장합니다.</t>
+    <t>본 영상은 2ch 스레드를 바탕으로, 피해자의 도를 넘은 악행 때문에 오히려 가해자에게 동정심이 생길 수밖에 없었던 충격적인 사건을 소개하는 영상입니다. 인간관계에서 발생하는 갈등의 양면성과 가해와 피해의 모호한 경계에 대해 다루며 시청자의 흥미를 자극하는 내용을 담고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 자극적인 인터넷 스레드를 기반으로 제작된 오락용 콘텐츠이므로 사실관계보다는 사건의 흥미로운 구성에 초점을 맞춰 시청하는 것이 좋습니다.</t>
   </si>
   <si>
     <t>【辺野古沖転覆事件】遺族が初会見…17歳の娘を失った両親が語った「告訴に踏み切った理由」【かなえ先生の切り抜き】元配信2026/08/01</t>
@@ -170,51 +170,33 @@
     <t>17:27</t>
   </si>
   <si>
-    <t>본 영상은 헤노코 앞바다 전복 사고로 17세 딸을 잃은 유족들이 처음으로 기자회견을 열고 고소에 이르게 된 경위와 심경을 밝힌 내용을 다룹니다. 가나에 선생은 사고의 사회적 맥락과 질의응답을 분석하며, 유족들이 직면한 부당한 압박과 평화 학습에 대한 우려 등 사건의 본질을 비판적으로 고찰합니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 감정적인 이슈를 다루는 영상이므로, 언론 보도와 사건의 맥락을 객관적인 시각에서 균형 있게 확인하는 태도가 필요합니다.</t>
+    <t>본 영상은 헤노코 해상에서 발생한 전복 사고로 17세 딸을 잃은 유족들이 처음으로 기자회견을 열고, 경찰에 고소장을 제출하게 된 배경과 심경을 밝히는 내용을 담고 있습니다. 카나에 선생은 사건의 경위와 유족들이 직면한 언론의 무례한 질문 및 사회적 갈등을 분석하며, 유족들의 고통과 진상 규명을 위한 절박함을 사회적 관점에서 조명합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 감정적인 주제와 민감한 사회적 이슈를 다루고 있으므로, 언론의 보도 태도나 질문 내용이 시청자에게 불쾌감을 줄 수 있음을 인지하고 시청하시기 바랍니다.</t>
   </si>
   <si>
     <t>미국</t>
   </si>
   <si>
-    <t>Three TASER Deployments That Ended Exactly as You'd Expect</t>
-  </si>
-  <si>
-    <t>Shane's Dumb Criminals</t>
-  </si>
-  <si>
-    <t>2026-07-29</t>
-  </si>
-  <si>
-    <t>16:26</t>
-  </si>
-  <si>
-    <t>본 영상은 경찰의 정당한 지시에 불응하고 도주를 시도하다가 결국 테이저건에 제압당하는 범죄자들의 사례 세 가지를 다룹니다. 자극적인 상황을 통해 법 집행관의 명령을 거부했을 때 발생하는 부정적인 결과와 테이저건의 강력한 위력을 실감 나게 보여주며, 잘못된 선택이 불러온 통쾌한 인과응보를 강조하는 블랙 코미디 형식의 콘텐츠입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 범죄 현장을 보여주며 시청자의 호기심을 유발하는 클릭베이트 형식의 채널이므로, 영상의 목적이 정보 전달보다는 단순 오락성에 있음을 인지하고 시청하십시오.</t>
+    <t>Nancy Guthrie Investigation: New Developments That Could Change The Trajectory Of This Case</t>
+  </si>
+  <si>
+    <t>BrewCrew Beyond 5-0</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>이 영상은 낸시 거스리 사건과 관련된 최근의 공적인 발언들이 수사의 흐름을 어떻게 바꿀 수 있는지 분석합니다. 오랜 기간 이어진 사건의 침묵 속에서 새로운 단서나 변화의 징후가 있는지 법적 관점에서 검토하며, 사건의 현주소와 향후 수사 방향성에 대해 의문을 제기하고 사실 관계를 명확히 하고자 합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 이 영상은 구체적인 증거보다는 공개된 발언에 의존한 추측성 분석일 가능성이 높으므로, 자극적인 제목에 현혹되지 말고 공식 수사 발표를 확인하는 것이 중요합니다.</t>
   </si>
   <si>
     <t>라이징스타</t>
   </si>
   <si>
-    <t>【大炎上】BYD軽EV、日本市場で総スカンどころか“壊滅的評価”！購入者が次々ドン引きした衝撃の理由とは…【ゆっくり解説】</t>
-  </si>
-  <si>
-    <t>未来の日本車</t>
-  </si>
-  <si>
-    <t>20:14</t>
-  </si>
-  <si>
-    <t>이 영상은 중국 전기차 브랜드 BYD가 일본 경형 EV 시장에 진출하며 겪은 부정적인 평가와 논란을 다룹니다. 특히 일본 소비자들이 기대했던 품질 및 안전 기준에 미치지 못하는 문제점들이 제기되며, 실제 구매자들 사이에서 발생하는 실망감과 제품 경쟁력에 대한 비판적 시각을 상세히 설명하고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 자극적인 제목과 비판적 논조를 사용하여 클릭을 유도하는 콘텐츠이므로, 정보의 객관성을 확보하기 위해 공식적인 차량 평가 데이터와 비교 확인하는 과정이 필요합니다.</t>
-  </si>
-  <si>
     <t>【大谷翔平】「この夕食の目的は歓迎だけじゃなかった」タリック・スクーバルが涙で語るドジャース初の親睦会、大谷翔平が全員へ贈った品の真意にファン感涙【海外の反応・MLB】</t>
   </si>
   <si>
@@ -224,10 +206,10 @@
     <t>27:53</t>
   </si>
   <si>
-    <t>다저스 이적 후 열린 팀 친목회에서 오타니 쇼헤이가 팀원들에게 특별한 선물을 전달하며 동료애를 다진 일화가 공개되었습니다. 단순한 환영을 넘어 팀의 결속력을 강조한 오타니의 진심에 타릭 스쿠발이 감동의 눈물을 흘렸으며, 이러한 행동은 국적과 입장을 뛰어넘어 진정한 원팀으로 거듭나려는 다저스의 끈끈한 유대 관계를 잘 보여주어 팬들에게 큰 울림을 주고 있습니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 본 영상은 선수의 감동적인 에피소드를 다루고 있으나, 클릭베이트 성격이 강한 자극적 제목을 사용하고 있으므로 사실 확인이 필요한 정보로 간주하고 시청하시기 바랍니다.</t>
+    <t>다저스 이적 후 열린 첫 팀 친목회에서 오타니 쇼헤이가 보여준 진심 어린 행동이 화제입니다. 단순한 환영회를 넘어 팀원들에게 특별한 선물을 전달하며 동료애를 다진 오타니의 모습에, 불안감을 느꼈던 타릭 스쿠발이 눈물을 흘리며 감동했습니다. 국적과 환경을 초월해 진정한 팀의 일원으로 받아들이는 오타니와 다저스 선수들의 끈끈한 유대 관계가 깊은 울림을 줍니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 해당 영상은 자극적인 제목과 썸네일을 활용한 유튜브 콘텐츠로, 사실관계보다는 감동적인 내러티브 중심의 해외 반응 요약 영상임을 유의하세요.</t>
   </si>
   <si>
     <t>【炎上】総理を批判したくて仕方がない蓮舫、ありえないデマに引っかかってしまう</t>
@@ -239,40 +221,55 @@
     <t>4:08</t>
   </si>
   <si>
-    <t>본 영상은 입헌민주당 렌호 의원이 총리를 비판하는 과정에서 잘못된 정보(데마)를 사실로 오인하여 지적했다가 오히려 역풍을 맞고 논란이 된 상황을 다룹니다. 정치적 공방 속에서 정보의 사실 관계 확인이 얼마나 중요한지 강조하며, 소셜 미디어를 통한 정치인들의 발언과 대중의 반응을 분석하는 내용입니다.</t>
-  </si>
-  <si>
-    <t>⚠️정치적 이슈를 다루는 유튜브 채널은 자극적인 제목과 썸네일을 통해 조회수를 유도하는 경우가 많으므로, 특정 정당이나 인물에 대한 정보를 접할 때 반드시 교차 검증을 거치는 것이 중요합니다.</t>
-  </si>
-  <si>
-    <t>【衝撃】シーハン炎上、1回3被弾で球場からブーイング…降板直後に明かされた矢田修氏の一言に全米注目！プライアーコーチが語った“大谷翔平とドジャースの本音”とは？</t>
-  </si>
-  <si>
-    <t>410-Nova</t>
-  </si>
-  <si>
-    <t>13:22</t>
-  </si>
-  <si>
-    <t>2026년 다저스의 3연패 도전 중, 투수 에메트 시한이 1이닝 3피홈런이라는 참담한 부진으로 홈팬들의 야유를 받으며 고전합니다. 절망에 빠진 그가 멘토 야다 오사무의 조언과 야마모토 요시노부의 격려를 통해 회복해 나가는 과정을 그렸으며, 랜디 존슨의 분석을 통해 투수 심리의 중요성을 다룹니다.</t>
-  </si>
-  <si>
-    <t>⚠️해당 영상은 실제 사실과 가상 시나리오가 혼합된 낚시성 제목을 사용하고 있으므로 정보 수용에 주의가 필요합니다.</t>
-  </si>
-  <si>
-    <t>【あらなみ切り抜き鑑賞】倉庫炎上事件に笑いが止まらない栞葉るり【栞葉るり切り抜き/にじさんじ切り抜き】</t>
-  </si>
-  <si>
-    <t>にじさんじのClips【にじさんじ切り抜き】</t>
-  </si>
-  <si>
-    <t>17:37</t>
-  </si>
-  <si>
-    <t>니지산지 소속 버추얼 라이버 시오리하 루리가 '아라나미 마인크래프트' 방송 중 발생한 창고 화재 사건을 회상하며 폭소를 멈추지 못하는 모습을 담은 클립입니다. 창고가 불타버린 당황스러운 상황을 유쾌하게 풀어내며, 그 외에도 '우먀미' 발언이나 침대 트리 등 방송 중 있었던 소소한 에피소드들을 함께 돌아보는 즐거운 하이라이트 영상입니다.</t>
-  </si>
-  <si>
-    <t>⚠️ 자극적인 화재 사건을 소재로 하고 있으나 실제로는 라이버의 유쾌한 리액션이 중심인 웃음 유발 영상입니다.</t>
+    <t>해당 영상은 입헌민주당의 렌호 의원이 총리를 비판하려는 과정에서 확인되지 않은 가짜 뉴스를 인용했다가 논란이 된 사건을 다룹니다. 영상은 정치적 이슈를 전달하는 형식을 취하고 있으나, 특정 정치인에 대한 비판적 관점을 강조하는 전형적인 유튜브 시사 해설물의 성격을 띱니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 유튜브 시사 채널은 클릭베이트성 제목을 사용하는 경우가 많으므로, 특정 정치인의 발언이나 사건을 확인할 때는 반드시 공신력 있는 언론 보도를 대조하여 팩트를 확인해야 합니다.</t>
+  </si>
+  <si>
+    <t>【炎上覚悟】ヒカルの落語を聴いたプロの落語家の忖度なしの感想！！</t>
+  </si>
+  <si>
+    <t>桂三四郎撮影処</t>
+  </si>
+  <si>
+    <t>18:56</t>
+  </si>
+  <si>
+    <t>유명 유튜버 히카루가 메이지좌에서 선보인 첫 라쿠고 공연에 대해 프로 라쿠고가 카츠라 산시로가 비판적인 시각으로 분석합니다. 단순 만담인지 전통 예술인지에 대한 논쟁을 다루며, 프로의 관점에서 그의 기술과 무대 매너를 평가하고 이것이 라쿠고계에 끼치는 영향과 의미를 가감 없이 논합니다.</t>
+  </si>
+  <si>
+    <t>⚠️ 유명인의 라쿠고 도전이 전통 예술의 확장인지 아니면 단순 화제성 유도인지에 대한 전문가의 냉정한 비평을 통해 예능과 예술의 경계에 대해 고민해볼 수 있습니다.</t>
+  </si>
+  <si>
+    <t>Brittney Griner Under Fire After Governor Responds to Controversial Claims About Caitlin Clark!</t>
+  </si>
+  <si>
+    <t>Clark Time Media</t>
+  </si>
+  <si>
+    <t>15:43</t>
+  </si>
+  <si>
+    <t>브리트니 그리너가 케이틀린 클라크를 향해 제기한 논란의 발언들에 대해 한 주지사가 강력한 대응을 예고하며 농구계에 큰 파장이 일고 있습니다. 해당 이슈는 온라인상에서 빠르게 확산하며 그리너의 주장에 대한 진위 여부와 그에 따른 후폭풍이 집중적인 논의의 대상이 되고 있습니다.</t>
+  </si>
+  <si>
+    <t>⚠️해당 영상은 제목과 내용이 자극적인 클릭베이트 형식을 띠고 있으므로, 공식 보도나 신뢰할 수 있는 스포츠 매체의 정보를 교차 검증하는 것이 좋습니다.</t>
+  </si>
+  <si>
+    <t>【海外の反応】「こんな絵文字読めない」日本人にしか理解できない"読み方"があると判明し世界の言語学者が絶句</t>
+  </si>
+  <si>
+    <t>日本大好きTV</t>
+  </si>
+  <si>
+    <t>31:44</t>
+  </si>
+  <si>
+    <t>독일 공항 로고가 일본인에게만 유독 '화난 표정'으로 인식된다는 사실에 호기심을 느낀 기호학자 아담이 일본을 방문합니다. 그는 1억 명의 일본인이 공통적으로 갖는 독특한 기호 해석 체계를 연구하며, 그 정답이 학술 논문이 아닌 일본 특유의 일상 문화와 아이들의 그림 속에 숨겨져 있다는 사실을 깨닫게 되는 과정을 다룹니다.</t>
+  </si>
+  <si>
+    <t>⚠️이 영상은 일본인만의 독특한 인식 체계를 강조하는 자극적인 제목과 설정을 활용한 홍보성 콘텐츠이므로 사실 확인이 필요합니다.</t>
   </si>
 </sst>
 </file>
@@ -359,11 +356,11 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -744,34 +741,34 @@
         <v>24</v>
       </c>
       <c r="I2" s="3">
-        <v>67208</v>
+        <v>129614</v>
       </c>
       <c r="J2" s="3">
-        <v>1227</v>
+        <v>1814</v>
       </c>
       <c r="K2" s="3">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="L2" s="3">
-        <v>29190</v>
+        <v>30408</v>
       </c>
       <c r="M2" s="3">
         <v>178000</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="O2" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="Q2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -788,46 +785,46 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="I3" s="3">
-        <v>23065</v>
+        <v>23492</v>
       </c>
       <c r="J3" s="3">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="K3" s="3">
         <v>59</v>
       </c>
       <c r="L3" s="3">
-        <v>3114</v>
+        <v>2916</v>
       </c>
       <c r="M3" s="3">
         <v>10500</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>35</v>
       </c>
       <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -856,34 +853,34 @@
         <v>39</v>
       </c>
       <c r="I4" s="3">
-        <v>35603</v>
+        <v>57104</v>
       </c>
       <c r="J4" s="3">
-        <v>1324</v>
+        <v>1676</v>
       </c>
       <c r="K4" s="3">
-        <v>220</v>
+        <v>282</v>
       </c>
       <c r="L4" s="3">
-        <v>22488</v>
+        <v>19290</v>
       </c>
       <c r="M4" s="3">
         <v>174000</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>41</v>
       </c>
       <c r="Q4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -912,34 +909,34 @@
         <v>45</v>
       </c>
       <c r="I5" s="3">
-        <v>43244</v>
+        <v>50834</v>
       </c>
       <c r="J5" s="3">
-        <v>1080</v>
+        <v>1238</v>
       </c>
       <c r="K5" s="3">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="L5" s="3">
-        <v>14146</v>
+        <v>12715</v>
       </c>
       <c r="M5" s="3">
         <v>271000</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>47</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -968,34 +965,34 @@
         <v>50</v>
       </c>
       <c r="I6" s="3">
-        <v>53002</v>
+        <v>55051</v>
       </c>
       <c r="J6" s="3">
-        <v>1486</v>
+        <v>1534</v>
       </c>
       <c r="K6" s="3">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L6" s="3">
-        <v>13004</v>
+        <v>11343</v>
       </c>
       <c r="M6" s="3">
         <v>174000</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>52</v>
       </c>
       <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:18">
@@ -1018,40 +1015,40 @@
         <v>55</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="3">
+        <v>21269</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1957</v>
+      </c>
+      <c r="K7" s="3">
+        <v>317</v>
+      </c>
+      <c r="L7" s="3">
+        <v>7497</v>
+      </c>
+      <c r="M7" s="3">
+        <v>35900</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I7" s="3">
-        <v>37685</v>
-      </c>
-      <c r="J7" s="3">
-        <v>4120</v>
-      </c>
-      <c r="K7" s="3">
-        <v>434</v>
-      </c>
-      <c r="L7" s="3">
-        <v>13282</v>
-      </c>
-      <c r="M7" s="3">
-        <v>92700</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="P7" s="4" t="s">
-        <v>59</v>
-      </c>
       <c r="Q7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1136,52 +1133,52 @@
         <v>36</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2">
         <v>1</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="I2" s="3">
-        <v>52889</v>
+        <v>90540</v>
       </c>
       <c r="J2" s="3">
-        <v>1403</v>
+        <v>746</v>
       </c>
       <c r="K2" s="3">
-        <v>263</v>
+        <v>52</v>
       </c>
       <c r="L2" s="3">
         <v>0</v>
       </c>
       <c r="M2" s="3">
-        <v>417</v>
-      </c>
-      <c r="N2" s="5">
-        <v>127</v>
-      </c>
-      <c r="O2" s="4" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N2" s="4">
+        <v>67</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="P2" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>65</v>
-      </c>
       <c r="Q2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:18">
@@ -1192,52 +1189,52 @@
         <v>36</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D3" s="2">
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I3" s="3">
-        <v>80175</v>
+        <v>108985</v>
       </c>
       <c r="J3" s="3">
-        <v>645</v>
+        <v>1429</v>
       </c>
       <c r="K3" s="3">
-        <v>46</v>
+        <v>390</v>
       </c>
       <c r="L3" s="3">
         <v>0</v>
       </c>
       <c r="M3" s="3">
-        <v>1280</v>
-      </c>
-      <c r="N3" s="5">
-        <v>63</v>
-      </c>
-      <c r="O3" s="4" t="s">
+        <v>1980</v>
+      </c>
+      <c r="N3" s="4">
+        <v>55</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="P3" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="P3" s="4" t="s">
-        <v>70</v>
-      </c>
       <c r="Q3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:18">
@@ -1248,52 +1245,52 @@
         <v>36</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D4" s="2">
         <v>3</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>23</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I4" s="3">
-        <v>69701</v>
+        <v>93468</v>
       </c>
       <c r="J4" s="3">
-        <v>1104</v>
+        <v>2543</v>
       </c>
       <c r="K4" s="3">
-        <v>305</v>
+        <v>397</v>
       </c>
       <c r="L4" s="3">
         <v>0</v>
       </c>
       <c r="M4" s="3">
-        <v>1960</v>
-      </c>
-      <c r="N4" s="5">
-        <v>36</v>
-      </c>
-      <c r="O4" s="4" t="s">
+        <v>3450</v>
+      </c>
+      <c r="N4" s="4">
+        <v>27</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="P4" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="P4" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="Q4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R4" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -1301,55 +1298,55 @@
         <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D5" s="2">
         <v>4</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="I5" s="3">
-        <v>60008</v>
+        <v>50760</v>
       </c>
       <c r="J5" s="3">
-        <v>2563</v>
+        <v>751</v>
       </c>
       <c r="K5" s="3">
-        <v>29</v>
+        <v>202</v>
       </c>
       <c r="L5" s="3">
         <v>0</v>
       </c>
       <c r="M5" s="3">
-        <v>1990</v>
-      </c>
-      <c r="N5" s="5">
-        <v>30</v>
-      </c>
-      <c r="O5" s="4" t="s">
+        <v>2890</v>
+      </c>
+      <c r="N5" s="4">
+        <v>18</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="P5" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="Q5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -1360,52 +1357,52 @@
         <v>36</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D6" s="2">
         <v>5</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="I6" s="3">
-        <v>50022</v>
+        <v>71488</v>
       </c>
       <c r="J6" s="3">
-        <v>716</v>
+        <v>642</v>
       </c>
       <c r="K6" s="3">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="L6" s="3">
         <v>0</v>
       </c>
       <c r="M6" s="3">
-        <v>8000</v>
-      </c>
-      <c r="N6" s="5">
-        <v>6</v>
-      </c>
-      <c r="O6" s="4" t="s">
+        <v>4180</v>
+      </c>
+      <c r="N6" s="4">
+        <v>17</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="P6" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="Q6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
